--- a/project-management/skills/pmo-pert-estimate/examples/scenario-4-cloud-migration/pert-estimate.xlsx
+++ b/project-management/skills/pmo-pert-estimate/examples/scenario-4-cloud-migration/pert-estimate.xlsx
@@ -7097,175 +7097,175 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>R06</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Scope creep from late-discovered applications not in original inventory</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
         <is>
           <t>1, 2</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="19">
         <f>E7*F7</f>
         <v/>
       </c>
-      <c r="H7">
+      <c r="H7" s="19">
         <f>IF(G7&gt;=15,"CRITICAL",IF(G7&gt;=10,"HIGH",IF(G7&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>Strict scope freeze after Phase 1 sign-off; formal change control board; contractual scope boundary clause</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="19">
         <f>L7*650</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Security compliance gap identified in hardened cloud environment</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Security</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>3, 4, 5, 6</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="19">
         <f>E8*F8</f>
         <v/>
       </c>
-      <c r="H8">
+      <c r="H8" s="19">
         <f>IF(G8&gt;=15,"CRITICAL",IF(G8&gt;=10,"HIGH",IF(G8&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="19" t="inlineStr">
         <is>
           <t>Cloud Security Posture Management (CSPM) tool from day one; automated policy-as-code enforcement; quarterly security reviews</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="19" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="19">
         <f>L8*650</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>R08</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Network performance degradation post-migration due to latency or bandwidth issues</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>4, 5, 6, 7</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="19">
         <f>E9*F9</f>
         <v/>
       </c>
-      <c r="H9">
+      <c r="H9" s="19">
         <f>IF(G9&gt;=15,"CRITICAL",IF(G9&gt;=10,"HIGH",IF(G9&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Network baseline measurement before migration; performance SLA defined; CDN and caching optimisation</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="19">
         <f>L9*650</f>
         <v/>
       </c>
@@ -7329,117 +7329,117 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Key personnel departure during critical migration waves</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Organizational</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>5, 6</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="19">
         <f>E11*F11</f>
         <v/>
       </c>
-      <c r="H11">
+      <c r="H11" s="19">
         <f>IF(G11&gt;=15,"CRITICAL",IF(G11&gt;=10,"HIGH",IF(G11&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>Knowledge documentation and runbooks maintained continuously; bench resource pre-identified; retention incentives</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L11" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="M11">
+      <c r="M11" s="19">
         <f>L11*650</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Third-party integrations not compatible with new cloud endpoints</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>4, 5, 6</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="19">
         <f>E12*F12</f>
         <v/>
       </c>
-      <c r="H12">
+      <c r="H12" s="19">
         <f>IF(G12&gt;=15,"CRITICAL",IF(G12&gt;=10,"HIGH",IF(G12&gt;=5,"MEDIUM","LOW")))</f>
         <v/>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>Mitigate</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="19" t="inlineStr">
         <is>
           <t>API contract testing in parallel with migration; stub servers for dependent systems; early vendor engagement</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="19" t="inlineStr">
         <is>
           <t>CA</t>
         </is>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="M12">
+      <c r="M12" s="19">
         <f>L12*650</f>
         <v/>
       </c>
